--- a/data/trans_camb/P20B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 53,41</t>
+          <t>-18,54; 52,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 39,93</t>
+          <t>-30,02; 40,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 27,74</t>
+          <t>-37,32; 29,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 44,39</t>
+          <t>15,36; 45,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 32,05</t>
+          <t>7,73; 34,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,64; 27,31</t>
+          <t>5,62; 29,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 41,65</t>
+          <t>3,59; 42,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 25,51</t>
+          <t>-7,98; 27,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 21,74</t>
+          <t>-14,92; 20,31</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 611,34</t>
+          <t>-40,68; 540,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 515,99</t>
+          <t>-70,85; 520,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 1074,99</t>
+          <t>2,02; 1078,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 639,38</t>
+          <t>-40,96; 983,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,02; —</t>
+          <t>-70,31; 590,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 27,64</t>
+          <t>-14,84; 27,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 37,69</t>
+          <t>-13,63; 37,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 40,34</t>
+          <t>-3,13; 41,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 21,71</t>
+          <t>-10,91; 21,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 24,33</t>
+          <t>-12,64; 24,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 29,63</t>
+          <t>-9,05; 28,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 19,33</t>
+          <t>-7,7; 19,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 23,06</t>
+          <t>-7,24; 23,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 31,51</t>
+          <t>-2,66; 30,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 346,4</t>
+          <t>-50,41; 378,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 459,98</t>
+          <t>-52,67; 467,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 481,65</t>
+          <t>-20,7; 464,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,5; 213,41</t>
+          <t>-41,3; 221,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 209,6</t>
+          <t>-52,29; 207,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 252,86</t>
+          <t>-40,81; 266,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 153,28</t>
+          <t>-31,02; 152,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 169,65</t>
+          <t>-32,09; 170,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 263,3</t>
+          <t>-9,28; 230,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 29,52</t>
+          <t>-32,55; 32,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,6; 49,15</t>
+          <t>-31,95; 48,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 51,01</t>
+          <t>-15,18; 52,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 34,92</t>
+          <t>-10,72; 35,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 29,65</t>
+          <t>-15,29; 28,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 25,11</t>
+          <t>-13,05; 24,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 27,83</t>
+          <t>-6,28; 27,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 28,04</t>
+          <t>-9,07; 28,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 31,45</t>
+          <t>-3,99; 31,62</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,45; —</t>
+          <t>-54,6; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,85; —</t>
+          <t>-71,89; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,41; —</t>
+          <t>-56,99; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 740,83</t>
+          <t>-31,53; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 695,84</t>
+          <t>-42,25; 830,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 742,82</t>
+          <t>-23,86; 849,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 33,83</t>
+          <t>-27,97; 33,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 39,09</t>
+          <t>-20,2; 39,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 51,23</t>
+          <t>-13,99; 48,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-38,58; 11,44</t>
+          <t>-38,49; 11,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 29,25</t>
+          <t>-31,59; 26,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 27,7</t>
+          <t>-31,07; 25,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,58; 11,42</t>
+          <t>-29,08; 13,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 23,4</t>
+          <t>-16,79; 24,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 26,61</t>
+          <t>-17,21; 26,55</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,15; 75,73</t>
+          <t>-78,06; 60,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 172,66</t>
+          <t>-62,44; 130,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 155,6</t>
+          <t>-63,09; 146,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,86; 69,77</t>
+          <t>-66,68; 91,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 137,29</t>
+          <t>-41,41; 158,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 167,17</t>
+          <t>-41,67; 179,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 61,94</t>
+          <t>-4,4; 63,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 70,0</t>
+          <t>-5,67; 70,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 70,22</t>
+          <t>-13,41; 68,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 47,9</t>
+          <t>0,85; 48,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 63,51</t>
+          <t>1,65; 62,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 26,11</t>
+          <t>-7,27; 27,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 44,5</t>
+          <t>6,5; 44,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,77; 57,45</t>
+          <t>5,55; 57,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 35,1</t>
+          <t>-2,07; 35,75</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 905,68</t>
+          <t>-24,8; 1052,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,03; —</t>
+          <t>-34,6; 1075,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 1049,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,87; 943,47</t>
+          <t>11,57; 1179,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,93; 1486,96</t>
+          <t>18,14; 1416,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 777,99</t>
+          <t>-25,1; 832,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-38,82; 39,51</t>
+          <t>-37,5; 39,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 35,68</t>
+          <t>-34,63; 35,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 18,39</t>
+          <t>-42,14; 17,67</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 16,17</t>
+          <t>-24,12; 15,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 32,27</t>
+          <t>-12,42; 32,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 12,63</t>
+          <t>-23,31; 13,76</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 17,17</t>
+          <t>-18,66; 18,54</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 27,46</t>
+          <t>-13,57; 26,5</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 11,88</t>
+          <t>-17,71; 12,87</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-79,14; 417,27</t>
+          <t>-78,46; 460,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 355,64</t>
+          <t>-67,41; 307,95</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-69,84; 168,67</t>
+          <t>-70,4; 153,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-82,96; 195,76</t>
+          <t>-86,86; 204,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 291,73</t>
+          <t>-48,5; 341,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 160,16</t>
+          <t>-80,51; 151,18</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 119,81</t>
+          <t>-61,5; 135,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 187,69</t>
+          <t>-42,42; 195,08</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 94,19</t>
+          <t>-52,56; 101,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 19,34</t>
+          <t>-30,37; 21,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 23,23</t>
+          <t>-29,6; 23,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 9,27</t>
+          <t>-32,83; 10,23</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 12,47</t>
+          <t>-20,38; 13,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 10,93</t>
+          <t>-22,53; 12,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 16,28</t>
+          <t>-15,92; 15,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 7,02</t>
+          <t>-18,85; 8,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 11,76</t>
+          <t>-18,17; 11,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 8,05</t>
+          <t>-17,45; 9,16</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-66,4; 84,83</t>
+          <t>-63,7; 92,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 94,4</t>
+          <t>-62,34; 87,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,94; 38,54</t>
+          <t>-67,51; 46,19</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 58,7</t>
+          <t>-56,49; 65,58</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-63,32; 49,27</t>
+          <t>-61,73; 62,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 88,31</t>
+          <t>-40,03; 74,23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 31,35</t>
+          <t>-47,23; 33,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 43,82</t>
+          <t>-47,27; 46,49</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 32,41</t>
+          <t>-44,66; 36,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 9,91</t>
+          <t>-31,65; 11,37</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 27,1</t>
+          <t>-15,16; 30,67</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 29,07</t>
+          <t>-18,89; 31,35</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 22,62</t>
+          <t>-9,13; 22,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 15,3</t>
+          <t>-15,34; 18,63</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 11,0</t>
+          <t>-18,2; 12,84</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 14,36</t>
+          <t>-11,98; 13,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 16,89</t>
+          <t>-9,15; 16,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 14,47</t>
+          <t>-11,46; 17,03</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-76,21; 83,75</t>
+          <t>-81,09; 111,59</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-49,32; 188,54</t>
+          <t>-42,17; 228,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 229,7</t>
+          <t>-50,96; 224,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,04; 196,36</t>
+          <t>-37,32; 217,7</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-65,87; 132,93</t>
+          <t>-59,29; 179,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,5; 106,3</t>
+          <t>-69,4; 141,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,17; 101,62</t>
+          <t>-43,01; 96,74</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 113,99</t>
+          <t>-36,85; 107,91</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-41,11; 96,4</t>
+          <t>-41,21; 113,55</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 13,26</t>
+          <t>-5,92; 13,3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 17,68</t>
+          <t>-3,07; 17,54</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 16,72</t>
+          <t>-3,62; 16,01</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 11,25</t>
+          <t>-2,65; 11,62</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 11,06</t>
+          <t>-3,43; 12,17</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,37</t>
+          <t>-4,76; 9,78</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,97</t>
+          <t>-1,67; 10,1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 11,73</t>
+          <t>-0,33; 11,75</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 11,33</t>
+          <t>-0,51; 11,17</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 62,52</t>
+          <t>-18,78; 65,53</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 80,31</t>
+          <t>-9,57; 86,94</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 85,3</t>
+          <t>-11,65; 75,41</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 71,67</t>
+          <t>-11,54; 68,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 67,62</t>
+          <t>-15,11; 75,03</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 56,77</t>
+          <t>-19,19; 58,48</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 50,26</t>
+          <t>-6,46; 52,8</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 60,56</t>
+          <t>-0,99; 61,44</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 58,96</t>
+          <t>-2,09; 57,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P20B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P20B-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-8,79</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>13,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>3,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 52,74</t>
+          <t>-14,08; 50,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 40,61</t>
+          <t>-29,98; 41,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 29,45</t>
+          <t>-45,19; 24,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 45,76</t>
+          <t>16,3; 46,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 34,21</t>
+          <t>5,66; 31,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 29,64</t>
+          <t>4,89; 26,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 42,04</t>
+          <t>5,72; 42,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 27,24</t>
+          <t>-10,12; 25,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 20,31</t>
+          <t>-14,49; 17,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-24,38%</t>
+          <t>-32,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 540,26</t>
+          <t>-34,72; 561,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 520,08</t>
+          <t>-70,96; 485,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 1078,93</t>
+          <t>14,42; 1139,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 983,73</t>
+          <t>-50,75; 648,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,31; 590,82</t>
+          <t>-75,15; 527,15</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,51</t>
+          <t>21,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,53</t>
+          <t>16,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 27,02</t>
+          <t>-13,31; 28,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 37,78</t>
+          <t>-14,36; 41,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 41,81</t>
+          <t>-2,6; 44,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 21,86</t>
+          <t>-11,47; 21,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 24,26</t>
+          <t>-13,13; 24,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 28,28</t>
+          <t>-9,91; 29,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 19,86</t>
+          <t>-6,25; 19,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 23,82</t>
+          <t>-5,56; 25,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 30,07</t>
+          <t>1,64; 32,65</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>106,93%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 378,11</t>
+          <t>-47,08; 352,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,67; 467,0</t>
+          <t>-59,56; 402,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 464,87</t>
+          <t>-10,79; 613,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 221,39</t>
+          <t>-42,74; 208,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 207,41</t>
+          <t>-55,54; 230,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 266,54</t>
+          <t>-40,72; 242,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 152,19</t>
+          <t>-26,34; 158,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 170,48</t>
+          <t>-25,22; 220,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 230,62</t>
+          <t>3,37; 260,9</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27,89</t>
+          <t>27,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,47</t>
+          <t>17,17</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 32,38</t>
+          <t>-31,71; 33,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 48,74</t>
+          <t>-23,08; 49,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 52,57</t>
+          <t>-8,88; 50,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 35,19</t>
+          <t>-10,75; 34,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 28,42</t>
+          <t>-15,93; 28,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 24,71</t>
+          <t>-12,38; 25,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 27,65</t>
+          <t>-6,4; 28,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 28,47</t>
+          <t>-8,7; 27,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 31,62</t>
+          <t>-2,67; 30,41</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216,63%</t>
+          <t>212,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>141,59%</t>
+          <t>139,23%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,6; —</t>
+          <t>-55,22; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,89; —</t>
+          <t>-63,09; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,99; —</t>
+          <t>-51,68; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,53; —</t>
+          <t>-36,22; 702,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 830,68</t>
+          <t>-49,83; 663,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 849,69</t>
+          <t>-16,23; 894,17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,17</t>
+          <t>25,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-4,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>5,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 33,56</t>
+          <t>-27,31; 34,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 39,54</t>
+          <t>-22,67; 40,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 48,72</t>
+          <t>-13,73; 52,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 11,59</t>
+          <t>-41,86; 8,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 26,24</t>
+          <t>-26,23; 28,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 25,15</t>
+          <t>-33,0; 24,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 13,1</t>
+          <t>-28,28; 10,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 24,48</t>
+          <t>-18,98; 24,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 26,55</t>
+          <t>-18,26; 26,05</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>184,37%</t>
+          <t>196,62%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-11,92%</t>
+          <t>-14,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,06; 60,95</t>
+          <t>-77,9; 56,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 130,7</t>
+          <t>-55,11; 157,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,09; 146,76</t>
+          <t>-66,37; 137,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 91,42</t>
+          <t>-70,17; 69,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 158,46</t>
+          <t>-45,23; 157,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 179,92</t>
+          <t>-45,88; 180,1</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32,33</t>
+          <t>33,32</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15,57</t>
+          <t>15,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 63,78</t>
+          <t>-1,39; 69,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 70,83</t>
+          <t>-10,77; 70,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 68,29</t>
+          <t>-8,93; 70,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 48,37</t>
+          <t>-0,47; 47,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 62,38</t>
+          <t>1,75; 63,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 27,12</t>
+          <t>-6,91; 25,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,5; 44,95</t>
+          <t>6,49; 46,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,55; 57,21</t>
+          <t>7,68; 57,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 35,75</t>
+          <t>-3,82; 34,62</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156,39%</t>
+          <t>161,18%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>158,14%</t>
+          <t>151,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>134,33%</t>
+          <t>132,56%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 1052,43</t>
+          <t>-15,34; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 1075,08</t>
+          <t>-47,51; 1178,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>-43,13; 1042,88</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,57; 1179,65</t>
+          <t>16,49; 1133,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>18,14; 1416,15</t>
+          <t>21,11; 1077,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 832,7</t>
+          <t>-38,84; 861,89</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-8,9</t>
+          <t>-9,39</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-4,26</t>
+          <t>-4,63</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-3,1</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 39,4</t>
+          <t>-39,82; 35,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 35,67</t>
+          <t>-35,4; 36,29</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 17,67</t>
+          <t>-43,02; 17,29</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 15,22</t>
+          <t>-22,04; 17,5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 32,86</t>
+          <t>-12,25; 35,86</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 13,76</t>
+          <t>-24,22; 13,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 18,54</t>
+          <t>-19,58; 18,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 26,5</t>
+          <t>-9,77; 28,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 12,87</t>
+          <t>-20,0; 11,29</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-25,75%</t>
+          <t>-27,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,88%</t>
+          <t>-23,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-11,09%</t>
+          <t>-13,29%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-78,46; 460,89</t>
+          <t>-79,57; 352,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 307,95</t>
+          <t>-69,62; 341,13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 153,99</t>
+          <t>-73,44; 172,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 204,76</t>
+          <t>-81,85; 178,23</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 341,51</t>
+          <t>-49,98; 343,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 151,18</t>
+          <t>-79,97; 171,37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-61,5; 135,45</t>
+          <t>-64,24; 143,25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 195,08</t>
+          <t>-35,16; 210,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 101,62</t>
+          <t>-57,85; 84,7</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-11,41</t>
+          <t>-12,26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,76</t>
+          <t>-4,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 21,5</t>
+          <t>-27,18; 19,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 23,21</t>
+          <t>-30,71; 23,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 10,23</t>
+          <t>-33,02; 6,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 13,75</t>
+          <t>-19,76; 14,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 12,21</t>
+          <t>-22,48; 12,96</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 15,02</t>
+          <t>-16,38; 15,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 8,33</t>
+          <t>-19,7; 8,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 11,49</t>
+          <t>-19,18; 10,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 9,16</t>
+          <t>-16,17; 8,54</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-30,95%</t>
+          <t>-33,24%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1,27%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-14,5%</t>
+          <t>-12,87%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 92,95</t>
+          <t>-60,15; 90,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 87,07</t>
+          <t>-67,84; 100,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-67,51; 46,19</t>
+          <t>-68,9; 30,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 65,58</t>
+          <t>-54,03; 67,81</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 62,67</t>
+          <t>-60,61; 54,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 74,23</t>
+          <t>-42,76; 76,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 33,3</t>
+          <t>-50,33; 34,59</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 46,49</t>
+          <t>-49,58; 37,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 36,04</t>
+          <t>-40,68; 34,16</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>7,71</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,58</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 11,37</t>
+          <t>-28,76; 11,89</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 30,67</t>
+          <t>-16,33; 28,11</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 31,35</t>
+          <t>-16,4; 31,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 22,83</t>
+          <t>-9,07; 22,73</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 18,63</t>
+          <t>-14,68; 17,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 12,84</t>
+          <t>-17,33; 12,75</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 13,61</t>
+          <t>-11,32; 13,28</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 16,71</t>
+          <t>-9,82; 16,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 17,03</t>
+          <t>-11,05; 15,33</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-19,06%</t>
+          <t>-20,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-81,09; 111,59</t>
+          <t>-78,36; 106,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 228,47</t>
+          <t>-44,88; 218,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 224,91</t>
+          <t>-47,09; 248,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 217,7</t>
+          <t>-39,84; 200,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 179,12</t>
+          <t>-60,99; 183,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-69,4; 141,72</t>
+          <t>-70,63; 108,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 96,74</t>
+          <t>-42,13; 91,96</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 107,91</t>
+          <t>-35,73; 106,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-41,21; 113,55</t>
+          <t>-41,16; 103,78</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>3,14</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,38</t>
+          <t>5,53</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 13,3</t>
+          <t>-6,01; 12,69</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 17,54</t>
+          <t>-2,92; 18,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 16,01</t>
+          <t>-3,1; 16,72</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 11,62</t>
+          <t>-2,61; 11,79</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 12,17</t>
+          <t>-3,2; 12,1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 9,78</t>
+          <t>-3,81; 10,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 10,1</t>
+          <t>-1,04; 9,68</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 11,75</t>
+          <t>-0,07; 12,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 11,17</t>
+          <t>-0,26; 11,18</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 65,53</t>
+          <t>-19,25; 59,09</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 86,94</t>
+          <t>-11,49; 83,04</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 75,41</t>
+          <t>-9,11; 84,18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 68,51</t>
+          <t>-11,73; 70,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 75,03</t>
+          <t>-14,13; 72,99</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 58,48</t>
+          <t>-14,98; 61,09</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 52,8</t>
+          <t>-4,21; 50,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 61,44</t>
+          <t>-0,56; 63,27</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 57,33</t>
+          <t>-1,13; 56,77</t>
         </is>
       </c>
     </row>
